--- a/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:37:32+00:00</t>
+    <t>2026-04-30T08:59:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-practitioner.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:59:13+00:00</t>
+    <t>2026-08-21T10:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -930,7 +930,7 @@
     <t>OID for the specific vbPK in Austria</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/ValueSet/at-core-vbpk</t>
+    <t>https://fhir.hl7.at/core/r4/ValueSet/at-core-vbpk</t>
   </si>
   <si>
     <t>Practitioner.identifier:vbPK.value</t>
@@ -1037,7 +1037,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address}
+    <t xml:space="preserve">Address {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address}
 </t>
   </si>
   <si>
@@ -1114,7 +1114,7 @@
     <t>AdministrativeGenderAddition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
 </t>
   </si>
   <si>
@@ -1640,7 +1640,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="98.24609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="85.5859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1655,7 +1655,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.04296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="46.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
